--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mediabrut_a_2021_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mediabrut_a_2021_aysen.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:23</t>
+    <t xml:space="preserve">2026-09-24 01:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -736,13 +736,13 @@
         <v>10</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.06</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.65</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="11">
@@ -759,13 +759,13 @@
         <v>10</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.7</v>
+        <v>-0.81</v>
       </c>
     </row>
     <row r="12">
@@ -782,13 +782,13 @@
         <v>10</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="13">
@@ -799,19 +799,19 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.32</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="14">
@@ -851,13 +851,13 @@
         <v>10</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.67</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16">
@@ -874,13 +874,13 @@
         <v>10</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>-0.46</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.84</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="17">
@@ -900,7 +900,7 @@
         <v>-0.03</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0.19</v>
